--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,8 +742,11 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,8 +774,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +806,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +884,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -896,8 +916,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +948,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,37 +961,41 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
         <v>200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
       </c>
       <c r="I17" s="3">
+        <v>300</v>
+      </c>
+      <c r="J17" s="3">
         <v>200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -973,28 +1003,31 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1039,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1018,25 +1052,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1064,8 +1101,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,37 +1133,43 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1197,11 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1421,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1366,54 +1436,60 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,8 +1616,9 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1539,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -1551,16 +1638,19 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,8 +1678,11 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1599,8 +1692,8 @@
       <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -1609,16 +1702,19 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,8 +1742,11 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1655,28 +1754,31 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
       </c>
       <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1684,28 +1786,31 @@
         <v>200</v>
       </c>
       <c r="E46" s="3">
+        <v>200</v>
+      </c>
+      <c r="F46" s="3">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>300</v>
       </c>
       <c r="H46" s="3">
         <v>300</v>
       </c>
       <c r="I46" s="3">
+        <v>300</v>
+      </c>
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,8 +1838,11 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1762,8 +1870,11 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1791,8 +1902,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="E52" s="3">
         <v>5500</v>
       </c>
       <c r="F52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>16100</v>
       </c>
       <c r="I52" s="3">
         <v>16100</v>
       </c>
       <c r="J52" s="3">
-        <v>106100</v>
+        <v>16100</v>
       </c>
       <c r="K52" s="3">
         <v>106100</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>106100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,25 +2092,26 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -1989,10 +2120,13 @@
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2020,8 +2154,11 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2049,25 +2186,28 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
       </c>
       <c r="I60" s="3">
         <v>100</v>
@@ -2076,10 +2216,13 @@
         <v>100</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2107,37 +2250,43 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E72" s="3">
         <v>5600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E76" s="3">
         <v>700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>98300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +2829,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2660,8 +2859,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="E89" s="3">
         <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
       </c>
       <c r="H89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,8 +3067,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2876,8 +3097,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>2200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>8400</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>90000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3209,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3239,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3335,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-8300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-90300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,8 +3399,11 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3168,15 +3420,18 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,88 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -745,16 +752,22 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -777,16 +790,22 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
@@ -809,8 +828,14 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +848,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +882,14 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +920,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +958,14 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +996,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +1013,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>200</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>100</v>
       </c>
       <c r="E18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-200</v>
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,40 +1105,48 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,31 +1177,37 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1136,40 +1215,52 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1291,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1329,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1443,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1481,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1519,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1557,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1671,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1772,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,8 +1788,10 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1626,31 +1799,37 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <v>100</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41" s="3">
+        <v>100</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,40 +1860,52 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1000</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,95 +1936,113 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>300</v>
+      </c>
+      <c r="F46" s="3">
         <v>200</v>
-      </c>
-      <c r="E46" s="3">
-        <v>200</v>
-      </c>
-      <c r="F46" s="3">
-        <v>100</v>
       </c>
       <c r="G46" s="3">
         <v>200</v>
       </c>
       <c r="H46" s="3">
+        <v>100</v>
+      </c>
+      <c r="I46" s="3">
+        <v>200</v>
+      </c>
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>600</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1100</v>
       </c>
       <c r="L46" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N46" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>22900</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>23500</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1841,31 +2050,37 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -1873,31 +2088,37 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -1905,8 +2126,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2164,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2202,52 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>3600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>7700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>16100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>16100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>106100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>106100</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2278,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F54" s="3">
         <v>3800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>107200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2336,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,63 +2352,71 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2157,16 +2424,22 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>900</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
@@ -2189,48 +2462,60 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2253,40 +2538,52 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>700</v>
+      </c>
+      <c r="F62" s="3">
         <v>4200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>5300</v>
       </c>
       <c r="J62" s="3">
         <v>4900</v>
       </c>
       <c r="K62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M62" s="3">
         <v>8800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2614,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2652,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2690,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
         <v>5400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2748,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2782,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2820,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2858,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2896,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>4900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2972,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3010,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +3048,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>98300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3124,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,31 +3225,33 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -2862,8 +3259,14 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3297,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3335,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3373,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3411,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3449,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,13 +3507,15 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3100,8 +3541,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3579,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3617,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>8400</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>90000</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3675,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3709,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3747,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3785,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3823,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-8300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-90300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,16 +3899,22 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -3423,15 +3926,21 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
@@ -746,8 +750,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -758,8 +762,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,10 +774,10 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
@@ -796,20 +803,23 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,8 +984,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,58 +1041,62 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1079,20 +1109,23 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1133,20 +1167,23 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1183,17 +1220,20 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1209,8 +1249,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1221,8 +1261,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1232,35 +1275,38 @@
       <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,8 +1384,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1346,35 +1398,38 @@
       <c r="E26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1384,35 +1439,38 @@
       <c r="E27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1589,20 +1659,23 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1612,35 +1685,38 @@
       <c r="E33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,8 +1753,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1688,78 +1767,84 @@
       <c r="E35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,28 +1876,29 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3">
         <v>100</v>
@@ -1820,16 +1907,19 @@
         <v>100</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,28 +1956,31 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -1896,16 +1989,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,8 +2038,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1954,34 +2053,37 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1989,37 +2091,40 @@
         <v>900</v>
       </c>
       <c r="E46" s="3">
+        <v>900</v>
+      </c>
+      <c r="F46" s="3">
         <v>300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>200</v>
       </c>
       <c r="G46" s="3">
         <v>200</v>
       </c>
       <c r="H46" s="3">
+        <v>200</v>
+      </c>
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>300</v>
       </c>
       <c r="K46" s="3">
         <v>300</v>
       </c>
       <c r="L46" s="3">
+        <v>300</v>
+      </c>
+      <c r="M46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2027,11 +2132,11 @@
         <v>22900</v>
       </c>
       <c r="E47" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F47" s="3">
         <v>23500</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2044,8 +2149,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2056,8 +2161,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2065,11 +2173,11 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2082,8 +2190,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2094,8 +2202,11 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2105,8 +2216,8 @@
       <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
+      <c r="F49" s="3">
+        <v>500</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
@@ -2120,8 +2231,8 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2132,8 +2243,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,8 +2325,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2220,34 +2340,37 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>3600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5500</v>
       </c>
       <c r="H52" s="3">
         <v>5500</v>
       </c>
       <c r="I52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J52" s="3">
         <v>7600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>16100</v>
       </c>
       <c r="L52" s="3">
         <v>16100</v>
       </c>
       <c r="M52" s="3">
-        <v>106100</v>
+        <v>16100</v>
       </c>
       <c r="N52" s="3">
         <v>106100</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>106100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,8 +2407,11 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2293,37 +2419,40 @@
         <v>13700</v>
       </c>
       <c r="E54" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F54" s="3">
         <v>13600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>107200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,8 +2484,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2366,22 +2497,22 @@
         <v>500</v>
       </c>
       <c r="F57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -2390,10 +2521,13 @@
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2401,11 +2535,11 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2418,8 +2552,8 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2430,20 +2564,23 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2468,34 +2605,37 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
-      </c>
-      <c r="K60" s="3">
-        <v>100</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
@@ -2504,22 +2644,25 @@
         <v>100</v>
       </c>
       <c r="N60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2544,8 +2687,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2553,37 +2699,40 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
+        <v>500</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3">
         <v>5400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1500</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
         <v>4900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E76" s="3">
         <v>10100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>98300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,51 +3319,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3184,35 +3379,38 @@
       <c r="E81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,17 +3425,18 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
@@ -3253,8 +3452,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3265,8 +3464,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-200</v>
       </c>
       <c r="H89" s="3">
         <v>-200</v>
       </c>
       <c r="I89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J89" s="3">
         <v>-100</v>
       </c>
       <c r="K89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3729,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,7 +3739,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -3547,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>1900</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>8400</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>90000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-8300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-90300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,8 +4154,11 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3914,11 +4166,11 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -3932,15 +4184,18 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,46 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
@@ -710,51 +711,54 @@
         <v>44926</v>
       </c>
       <c r="K7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>400</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -765,31 +769,34 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -806,31 +813,34 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>400</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,31 +963,34 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1068,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1051,81 +1078,87 @@
         <v>300</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H17" s="3">
         <v>200</v>
       </c>
       <c r="I17" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J17" s="3">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>300</v>
       </c>
       <c r="L17" s="3">
         <v>300</v>
       </c>
       <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E18" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,19 +1174,20 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-200</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
@@ -1161,52 +1195,55 @@
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1232,28 +1272,28 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>500</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1264,72 +1304,78 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>100</v>
       </c>
       <c r="G23" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H23" s="3">
         <v>-200</v>
       </c>
       <c r="I23" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F26" s="3">
+        <v>100</v>
       </c>
       <c r="G26" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H26" s="3">
         <v>-200</v>
       </c>
       <c r="I26" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>100</v>
       </c>
       <c r="G27" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H27" s="3">
         <v>-200</v>
       </c>
       <c r="I27" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,19 +1700,22 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
@@ -1653,70 +1723,76 @@
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F33" s="3">
+        <v>100</v>
       </c>
       <c r="G33" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H33" s="3">
         <v>-200</v>
       </c>
       <c r="I33" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,65 +1832,71 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="3">
+        <v>100</v>
       </c>
       <c r="G35" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H35" s="3">
         <v>-200</v>
       </c>
       <c r="I35" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
@@ -1829,22 +1911,25 @@
         <v>44926</v>
       </c>
       <c r="K38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,31 +1963,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>100</v>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H41" s="3">
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
@@ -1910,16 +1997,19 @@
         <v>100</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,31 +2049,34 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>900</v>
       </c>
       <c r="F43" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1992,39 +2085,42 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,49 +2137,55 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2094,66 +2196,69 @@
         <v>900</v>
       </c>
       <c r="F46" s="3">
-        <v>300</v>
-      </c>
-      <c r="G46" s="3">
+        <v>900</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
+        <v>100</v>
+      </c>
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
+        <v>500</v>
+      </c>
+      <c r="K46" s="3">
         <v>200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>200</v>
-      </c>
-      <c r="K46" s="3">
-        <v>300</v>
       </c>
       <c r="L46" s="3">
         <v>300</v>
       </c>
       <c r="M46" s="3">
+        <v>300</v>
+      </c>
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>22900</v>
+        <v>10200</v>
       </c>
       <c r="E47" s="3">
-        <v>22900</v>
+        <v>10100</v>
       </c>
       <c r="F47" s="3">
-        <v>23500</v>
+        <v>10100</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>10100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>10100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2164,8 +2269,11 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2176,25 +2284,25 @@
         <v>400</v>
       </c>
       <c r="F48" s="3">
+        <v>400</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="I48" s="3">
+        <v>500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2205,13 +2313,16 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
@@ -2219,23 +2330,23 @@
       <c r="F49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2342,35 +2462,38 @@
       <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
-        <v>3600</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
-        <v>5500</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>5500</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
         <v>7600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>16100</v>
       </c>
       <c r="M52" s="3">
         <v>16100</v>
       </c>
       <c r="N52" s="3">
-        <v>106100</v>
+        <v>16100</v>
       </c>
       <c r="O52" s="3">
         <v>106100</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>106100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>13700</v>
+        <v>15400</v>
       </c>
       <c r="E54" s="3">
         <v>13700</v>
       </c>
       <c r="F54" s="3">
-        <v>13600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>3800</v>
+        <v>13700</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H54" s="3">
-        <v>5700</v>
+        <v>13200</v>
       </c>
       <c r="I54" s="3">
-        <v>5500</v>
+        <v>12700</v>
       </c>
       <c r="J54" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K54" s="3">
         <v>7800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,8 +2615,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2499,23 +2630,23 @@
       <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>800</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -2524,39 +2655,42 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
       </c>
       <c r="F58" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2567,19 +2701,22 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
-      </c>
-      <c r="E59" s="3">
-        <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>900</v>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
@@ -2608,37 +2745,40 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>1100</v>
       </c>
       <c r="E60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1200</v>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I60" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J60" s="3">
         <v>500</v>
       </c>
       <c r="K60" s="3">
+        <v>500</v>
+      </c>
+      <c r="L60" s="3">
         <v>400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>100</v>
       </c>
       <c r="M60" s="3">
         <v>100</v>
@@ -2647,33 +2787,36 @@
         <v>100</v>
       </c>
       <c r="O60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="F61" s="3">
-        <v>300</v>
+        <v>2100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2690,49 +2833,55 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3900</v>
+        <v>100</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M66" s="3">
         <v>5400</v>
       </c>
-      <c r="H66" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>5400</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,13 +3159,16 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E72" s="3">
-        <v>1500</v>
+        <v>1300</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="3">
-        <v>4900</v>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H72" s="3">
-        <v>5600</v>
+        <v>-3200</v>
       </c>
       <c r="I72" s="3">
-        <v>5800</v>
+        <v>-3000</v>
       </c>
       <c r="J72" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K72" s="3">
         <v>6200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10100</v>
       </c>
-      <c r="F76" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-1600</v>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H76" s="3">
-        <v>700</v>
+        <v>7700</v>
       </c>
       <c r="I76" s="3">
-        <v>900</v>
+        <v>7900</v>
       </c>
       <c r="J76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K76" s="3">
         <v>3600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>98300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,24 +3511,27 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
@@ -3354,63 +3546,69 @@
         <v>44926</v>
       </c>
       <c r="K80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F81" s="3">
+        <v>100</v>
       </c>
       <c r="G81" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="H81" s="3">
         <v>-200</v>
       </c>
       <c r="I81" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,19 +3624,20 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
@@ -3455,8 +3654,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1800</v>
-      </c>
       <c r="G89" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
       </c>
       <c r="L89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,31 +3950,32 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G94" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="I94" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>8400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>90000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,72 +4318,78 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
-        <v>10700</v>
-      </c>
       <c r="G100" s="3">
-        <v>-2100</v>
+        <v>300</v>
       </c>
       <c r="H100" s="3">
-        <v>300</v>
+        <v>2600</v>
       </c>
       <c r="I100" s="3">
-        <v>-2000</v>
+        <v>-2200</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-8300</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-90300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
         <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -665,10 +665,10 @@
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -699,16 +699,16 @@
         <v>45382</v>
       </c>
       <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
@@ -781,19 +781,19 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -828,16 +828,16 @@
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -983,14 +983,14 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
         <v>200</v>
@@ -1122,7 +1122,7 @@
         <v>-200</v>
       </c>
       <c r="E18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1189,8 +1189,8 @@
       <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3">
+        <v>200</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
@@ -1234,13 +1234,13 @@
         <v>200</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
@@ -1278,7 +1278,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
@@ -1287,7 +1287,7 @@
         <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1316,22 +1316,22 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G23" s="3">
         <v>-300</v>
       </c>
       <c r="H23" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I23" s="3">
         <v>-300</v>
       </c>
       <c r="J23" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>800</v>
@@ -1448,22 +1448,22 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G26" s="3">
         <v>-300</v>
       </c>
       <c r="H26" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I26" s="3">
         <v>-300</v>
       </c>
       <c r="J26" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K26" s="3">
         <v>800</v>
@@ -1492,22 +1492,22 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3">
         <v>-300</v>
       </c>
       <c r="H27" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I27" s="3">
         <v>-300</v>
       </c>
       <c r="J27" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K27" s="3">
         <v>800</v>
@@ -1717,8 +1717,8 @@
       <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
+      <c r="G32" s="3">
+        <v>-200</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
@@ -1756,22 +1756,22 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3">
         <v>-300</v>
       </c>
       <c r="H33" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I33" s="3">
         <v>-300</v>
       </c>
       <c r="J33" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K33" s="3">
         <v>800</v>
@@ -1844,22 +1844,22 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G35" s="3">
         <v>-300</v>
       </c>
       <c r="H35" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I35" s="3">
         <v>-300</v>
       </c>
       <c r="J35" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K35" s="3">
         <v>800</v>
@@ -1899,16 +1899,16 @@
         <v>45382</v>
       </c>
       <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
@@ -1978,17 +1978,17 @@
       <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
-      </c>
-      <c r="J41" s="3">
-        <v>400</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
@@ -2061,22 +2061,22 @@
         <v>700</v>
       </c>
       <c r="E43" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F43" s="3">
-        <v>800</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2193,22 +2193,22 @@
         <v>900</v>
       </c>
       <c r="E46" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F46" s="3">
-        <v>900</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3">
+        <v>800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>700</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>500</v>
       </c>
       <c r="K46" s="3">
         <v>200</v>
@@ -2237,16 +2237,16 @@
         <v>10200</v>
       </c>
       <c r="E47" s="3">
-        <v>10100</v>
+        <v>10200</v>
       </c>
       <c r="F47" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3">
-        <v>10100</v>
+        <v>10200</v>
+      </c>
+      <c r="G47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I47" s="3">
         <v>10100</v>
@@ -2286,17 +2286,17 @@
       <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
-        <v>500</v>
+      <c r="G48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I48" s="3">
         <v>500</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -2325,22 +2325,22 @@
         <v>2000</v>
       </c>
       <c r="E49" s="3">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="F49" s="3">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H49" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>600</v>
       </c>
       <c r="J49" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -2462,11 +2462,11 @@
       <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
@@ -2545,22 +2545,22 @@
         <v>15400</v>
       </c>
       <c r="E54" s="3">
-        <v>13700</v>
+        <v>15200</v>
       </c>
       <c r="F54" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3">
+        <v>15100</v>
+      </c>
+      <c r="G54" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
         <v>13200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12700</v>
-      </c>
-      <c r="J54" s="3">
-        <v>12500</v>
       </c>
       <c r="K54" s="3">
         <v>7800</v>
@@ -2630,8 +2630,8 @@
       <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
+      <c r="G57" s="3">
+        <v>500</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
@@ -2712,14 +2712,14 @@
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
@@ -2760,19 +2760,19 @@
         <v>1500</v>
       </c>
       <c r="F60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>500</v>
       </c>
       <c r="K60" s="3">
         <v>500</v>
@@ -2801,22 +2801,22 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F61" s="3">
         <v>2100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2850,17 +2850,17 @@
       <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>300</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3">
         <v>3700</v>
@@ -3021,22 +3021,22 @@
         <v>1800</v>
       </c>
       <c r="E66" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="F66" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
         <v>5500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>4300</v>
       </c>
       <c r="K66" s="3">
         <v>4200</v>
@@ -3261,20 +3261,20 @@
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="F72" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>-3200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-2700</v>
       </c>
       <c r="K72" s="3">
         <v>6200</v>
@@ -3435,22 +3435,22 @@
         <v>12000</v>
       </c>
       <c r="E76" s="3">
-        <v>10600</v>
+        <v>12200</v>
       </c>
       <c r="F76" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G76" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
         <v>7700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>8200</v>
       </c>
       <c r="K76" s="3">
         <v>3600</v>
@@ -3534,16 +3534,16 @@
         <v>45382</v>
       </c>
       <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
@@ -3572,22 +3572,22 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G81" s="3">
         <v>-300</v>
       </c>
       <c r="H81" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I81" s="3">
         <v>-300</v>
       </c>
       <c r="J81" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="K81" s="3">
         <v>800</v>
@@ -3630,17 +3630,17 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>4</v>
@@ -3904,16 +3904,16 @@
         <v>-600</v>
       </c>
       <c r="G89" s="3">
+        <v>200</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>200</v>
+        <v>-400</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
@@ -4098,16 +4098,16 @@
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>2100</v>
+        <v>-400</v>
       </c>
       <c r="J94" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
         <v>100</v>
@@ -4336,16 +4336,16 @@
         <v>600</v>
       </c>
       <c r="G100" s="3">
+        <v>200</v>
+      </c>
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
-        <v>2600</v>
-      </c>
       <c r="I100" s="3">
-        <v>-2200</v>
+        <v>400</v>
       </c>
       <c r="J100" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4424,16 +4424,16 @@
         <v>-100</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-100</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,97 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
@@ -754,17 +761,17 @@
       <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -772,13 +779,19 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -798,11 +811,11 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -816,25 +829,31 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
-        <v>100</v>
-      </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -842,11 +861,11 @@
       <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -860,8 +879,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +999,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -980,11 +1019,11 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1010,8 +1049,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,25 +1120,27 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>300</v>
+      </c>
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
       </c>
       <c r="I17" s="3">
         <v>200</v>
@@ -1096,42 +1149,48 @@
         <v>200</v>
       </c>
       <c r="K17" s="3">
+        <v>200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
-      </c>
-      <c r="M17" s="3">
-        <v>300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>200</v>
       </c>
       <c r="O17" s="3">
         <v>300</v>
       </c>
       <c r="P17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>300</v>
+      </c>
+      <c r="R17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
       </c>
       <c r="G18" s="3">
         <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>-100</v>
@@ -1139,26 +1198,32 @@
       <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-200</v>
+      <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O18" s="3">
         <v>-300</v>
       </c>
       <c r="P18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1240,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1187,40 +1254,46 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1231,26 +1304,26 @@
         <v>-100</v>
       </c>
       <c r="F21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1263,8 +1336,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1275,31 +1354,31 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>200</v>
+      </c>
+      <c r="L22" s="3">
+        <v>200</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1307,8 +1386,14 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1316,16 +1401,16 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H23" s="3">
         <v>200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-300</v>
       </c>
       <c r="I23" s="3">
         <v>-300</v>
@@ -1334,25 +1419,31 @@
         <v>-300</v>
       </c>
       <c r="K23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,11 +1468,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1395,8 +1486,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1536,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1448,16 +1551,16 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H26" s="3">
         <v>200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-300</v>
       </c>
       <c r="I26" s="3">
         <v>-300</v>
@@ -1466,25 +1569,31 @@
         <v>-300</v>
       </c>
       <c r="K26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1492,16 +1601,16 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H27" s="3">
         <v>200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-300</v>
       </c>
       <c r="I27" s="3">
         <v>-300</v>
@@ -1510,25 +1619,31 @@
         <v>-300</v>
       </c>
       <c r="K27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1836,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1715,40 +1854,46 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1756,16 +1901,16 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H33" s="3">
         <v>200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-300</v>
       </c>
       <c r="I33" s="3">
         <v>-300</v>
@@ -1774,25 +1919,31 @@
         <v>-300</v>
       </c>
       <c r="K33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1986,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1844,16 +2001,16 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H35" s="3">
         <v>200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-300</v>
       </c>
       <c r="I35" s="3">
         <v>-300</v>
@@ -1862,74 +2019,86 @@
         <v>-300</v>
       </c>
       <c r="K35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,8 +2135,10 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1973,43 +2146,49 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
-        <v>100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>200</v>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M41" s="3">
         <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
+        <v>100</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,31 +2231,37 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>600</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2088,16 +2273,22 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2122,11 +2313,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2140,8 +2331,14 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2166,70 +2363,82 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="E46" s="3">
         <v>800</v>
       </c>
       <c r="F46" s="3">
+        <v>900</v>
+      </c>
+      <c r="G46" s="3">
         <v>800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>800</v>
+      </c>
+      <c r="I46" s="3">
         <v>700</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>600</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1100</v>
       </c>
       <c r="P46" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R46" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2245,26 +2454,26 @@
       <c r="G47" s="3">
         <v>10200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3">
+        <v>10200</v>
       </c>
       <c r="I47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>10100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2272,8 +2481,14 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2289,26 +2504,26 @@
       <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
+      <c r="H48" s="3">
+        <v>400</v>
       </c>
       <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2316,8 +2531,14 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2325,34 +2546,34 @@
         <v>2000</v>
       </c>
       <c r="E49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G49" s="3">
         <v>1900</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2360,8 +2581,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2681,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2465,35 +2704,41 @@
       <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
+        <v>200</v>
+      </c>
+      <c r="M52" s="3">
         <v>7600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>7700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>16100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>16100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>106100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>106100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F54" s="3">
         <v>15400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>15100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>15000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>13200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>16400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>107200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,13 +2875,15 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E57" s="3">
         <v>500</v>
@@ -2633,35 +2894,41 @@
       <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
+        <v>500</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2669,34 +2936,34 @@
         <v>300</v>
       </c>
       <c r="E58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2704,13 +2971,19 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -2721,11 +2994,11 @@
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
@@ -2748,52 +3021,64 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>100</v>
       </c>
       <c r="O60" s="3">
         <v>100</v>
       </c>
       <c r="P60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>100</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2801,29 +3086,29 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>300</v>
+      </c>
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>4700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +3121,64 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
       </c>
       <c r="F62" s="3">
+        <v>400</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>100</v>
+      </c>
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>3700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>5300</v>
       </c>
       <c r="N62" s="3">
         <v>4900</v>
       </c>
       <c r="O62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q62" s="3">
         <v>8800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>5500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>8900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,20 +3491,26 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E70" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F70" s="3">
         <v>1500</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3591,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F72" s="3">
         <v>1300</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>1500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-3200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>6000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E76" s="3">
         <v>12000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G76" s="3">
         <v>12200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>7700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>98300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3891,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3572,16 +3961,16 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H81" s="3">
         <v>200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-300</v>
       </c>
       <c r="I81" s="3">
         <v>-300</v>
@@ -3590,25 +3979,31 @@
         <v>-300</v>
       </c>
       <c r="K81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +4020,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3642,11 +4039,11 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -3657,11 +4054,11 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -3669,8 +4066,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F89" s="3">
         <v>1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3977,11 +4418,11 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3995,8 +4436,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>8400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>90000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,11 +4638,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>400</v>
       </c>
       <c r="J100" s="3">
         <v>300</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L100" s="3">
+        <v>300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-8300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-90300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,11 +4888,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4409,48 +4906,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,107 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>100</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
@@ -767,14 +771,14 @@
       <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
+      <c r="M8" s="3">
+        <v>100</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -785,17 +789,20 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="3">
         <v>700</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
@@ -817,8 +824,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -835,28 +842,31 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -867,8 +877,8 @@
       <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>100</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1025,8 +1045,8 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,28 +1148,29 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>300</v>
       </c>
       <c r="F17" s="3">
         <v>300</v>
       </c>
       <c r="G17" s="3">
+        <v>300</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>200</v>
       </c>
       <c r="J17" s="3">
         <v>200</v>
@@ -1155,45 +1182,48 @@
         <v>200</v>
       </c>
       <c r="M17" s="3">
+        <v>200</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>300</v>
       </c>
       <c r="O17" s="3">
         <v>300</v>
       </c>
       <c r="P17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1204,26 +1234,29 @@
       <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
+      <c r="M18" s="3">
+        <v>-100</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1260,40 +1294,43 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1310,23 +1347,23 @@
         <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1360,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
@@ -1374,14 +1414,14 @@
       <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>200</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1392,28 +1432,31 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
         <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-300</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
@@ -1425,25 +1468,28 @@
         <v>-300</v>
       </c>
       <c r="M23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1474,8 +1520,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,28 +1591,31 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
         <v>-100</v>
       </c>
       <c r="H26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I26" s="3">
         <v>200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-300</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
@@ -1575,45 +1627,48 @@
         <v>-300</v>
       </c>
       <c r="M26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
         <v>-100</v>
       </c>
       <c r="H27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I27" s="3">
         <v>200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-300</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
@@ -1625,25 +1680,28 @@
         <v>-300</v>
       </c>
       <c r="M27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1860,60 +1930,63 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
         <v>-100</v>
       </c>
       <c r="H33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="3">
         <v>200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-300</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
@@ -1925,25 +1998,28 @@
         <v>-300</v>
       </c>
       <c r="M33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,28 +2068,31 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
         <v>-100</v>
       </c>
       <c r="H35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I35" s="3">
         <v>200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-300</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
@@ -2025,80 +2104,86 @@
         <v>-300</v>
       </c>
       <c r="M35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,8 +2223,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2152,25 +2239,25 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>100</v>
       </c>
       <c r="N41" s="3">
         <v>100</v>
@@ -2179,16 +2266,19 @@
         <v>100</v>
       </c>
       <c r="P41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,34 +2327,37 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>700</v>
       </c>
       <c r="G43" s="3">
         <v>700</v>
       </c>
       <c r="H43" s="3">
+        <v>700</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2279,16 +2372,19 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>700</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2319,8 +2415,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2369,76 +2468,82 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>800</v>
       </c>
       <c r="H46" s="3">
         <v>800</v>
       </c>
       <c r="I46" s="3">
+        <v>800</v>
+      </c>
+      <c r="J46" s="3">
         <v>700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>200</v>
       </c>
       <c r="M46" s="3">
         <v>200</v>
       </c>
       <c r="N46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
       </c>
       <c r="P46" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2460,23 +2565,23 @@
       <c r="I47" s="3">
         <v>10200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
-        <v>10100</v>
+      <c r="J47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>10100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
+      <c r="M47" s="3">
+        <v>10100</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2487,13 +2592,16 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>400</v>
@@ -2510,23 +2618,23 @@
       <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
-        <v>500</v>
+      <c r="J48" s="3">
+        <v>400</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
+      <c r="M48" s="3">
+        <v>500</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2537,13 +2645,16 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E49" s="3">
         <v>2000</v>
@@ -2552,7 +2663,7 @@
         <v>2000</v>
       </c>
       <c r="G49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="3">
         <v>1900</v>
@@ -2561,22 +2672,22 @@
         <v>1900</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K49" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
+      <c r="M49" s="3">
+        <v>600</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2710,35 +2830,38 @@
       <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
         <v>7600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>16100</v>
       </c>
       <c r="P52" s="3">
         <v>16100</v>
       </c>
       <c r="Q52" s="3">
-        <v>106100</v>
+        <v>16100</v>
       </c>
       <c r="R52" s="3">
         <v>106100</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>106100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E54" s="3">
         <v>15700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>13200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>107200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,16 +3007,17 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
@@ -2900,8 +3031,8 @@
       <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="J57" s="3">
+        <v>500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -2909,14 +3040,14 @@
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -2925,10 +3056,13 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2942,13 +3076,13 @@
         <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2959,14 +3093,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2977,16 +3111,19 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -3000,8 +3137,8 @@
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -3027,46 +3164,49 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
-      </c>
-      <c r="O60" s="3">
-        <v>100</v>
       </c>
       <c r="P60" s="3">
         <v>100</v>
@@ -3075,10 +3215,13 @@
         <v>100</v>
       </c>
       <c r="R60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3092,26 +3235,26 @@
         <v>300</v>
       </c>
       <c r="G61" s="3">
+        <v>300</v>
+      </c>
+      <c r="H61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>4700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,8 +3270,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3139,46 +3285,49 @@
         <v>100</v>
       </c>
       <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
       <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>5500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,23 +3662,26 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E70" s="3">
         <v>2000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1500</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E72" s="3">
         <v>1200</v>
       </c>
       <c r="F72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G72" s="3">
         <v>1300</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>1500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-3200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11900</v>
-      </c>
-      <c r="E76" s="3">
-        <v>12000</v>
       </c>
       <c r="F76" s="3">
         <v>12000</v>
       </c>
       <c r="G76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H76" s="3">
         <v>12200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>7700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>98300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,83 +4086,89 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
         <v>-100</v>
       </c>
       <c r="H81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="3">
         <v>200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-300</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
@@ -3985,25 +4180,28 @@
         <v>-300</v>
       </c>
       <c r="M81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4045,8 +4244,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -4060,8 +4259,8 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1500</v>
       </c>
-      <c r="G89" s="3">
-        <v>-100</v>
-      </c>
       <c r="H89" s="3">
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4424,8 +4645,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>90000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,13 +4845,14 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
@@ -4644,8 +4878,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I100" s="3">
+        <v>300</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-8300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-90300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4894,8 +5143,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4912,8 +5161,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4924,42 +5176,45 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RMCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>RMCO</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F8" s="3">
         <v>1300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
-      </c>
-      <c r="L8" s="3">
-        <v>100</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
@@ -781,17 +788,17 @@
       <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -799,26 +806,32 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
@@ -837,11 +850,11 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -855,37 +868,43 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>200</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
       </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
@@ -893,11 +912,11 @@
       <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -911,8 +930,14 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +958,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1071,11 +1110,11 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1101,8 +1140,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,37 +1227,39 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="E17" s="3">
         <v>1400</v>
       </c>
       <c r="F17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>200</v>
       </c>
       <c r="M17" s="3">
         <v>200</v>
@@ -1215,25 +1268,31 @@
         <v>200</v>
       </c>
       <c r="O17" s="3">
+        <v>200</v>
+      </c>
+      <c r="P17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>300</v>
-      </c>
-      <c r="R17" s="3">
-        <v>200</v>
       </c>
       <c r="S17" s="3">
         <v>300</v>
       </c>
       <c r="T17" s="3">
+        <v>200</v>
+      </c>
+      <c r="U17" s="3">
+        <v>300</v>
+      </c>
+      <c r="V17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1250,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>-100</v>
@@ -1270,26 +1329,32 @@
       <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-200</v>
+      <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S18" s="3">
         <v>-300</v>
       </c>
       <c r="T18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,20 +1375,22 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1334,51 +1401,57 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-100</v>
       </c>
       <c r="G21" s="3">
         <v>-100</v>
@@ -1390,26 +1463,26 @@
         <v>-100</v>
       </c>
       <c r="J21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1422,8 +1495,14 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1446,31 +1525,31 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>200</v>
+      </c>
+      <c r="P22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1478,19 +1557,25 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-200</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-100</v>
       </c>
       <c r="G23" s="3">
         <v>0</v>
@@ -1499,16 +1584,16 @@
         <v>-100</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
       </c>
       <c r="M23" s="3">
         <v>-300</v>
@@ -1517,25 +1602,31 @@
         <v>-300</v>
       </c>
       <c r="O23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1572,11 +1663,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1590,8 +1681,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,19 +1743,25 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-100</v>
       </c>
       <c r="G26" s="3">
         <v>0</v>
@@ -1667,16 +1770,16 @@
         <v>-100</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
         <v>200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
       </c>
       <c r="M26" s="3">
         <v>-300</v>
@@ -1685,36 +1788,42 @@
         <v>-300</v>
       </c>
       <c r="O26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-100</v>
       </c>
       <c r="G27" s="3">
         <v>0</v>
@@ -1723,16 +1832,16 @@
         <v>-100</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-300</v>
       </c>
       <c r="M27" s="3">
         <v>-300</v>
@@ -1741,25 +1850,31 @@
         <v>-300</v>
       </c>
       <c r="O27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,20 +2115,26 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2006,51 +2145,57 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-100</v>
       </c>
       <c r="G33" s="3">
         <v>0</v>
@@ -2059,16 +2204,16 @@
         <v>-100</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-300</v>
       </c>
       <c r="M33" s="3">
         <v>-300</v>
@@ -2077,25 +2222,31 @@
         <v>-300</v>
       </c>
       <c r="O33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,19 +2301,25 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-100</v>
       </c>
       <c r="G35" s="3">
         <v>0</v>
@@ -2171,16 +2328,16 @@
         <v>-100</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-300</v>
       </c>
       <c r="M35" s="3">
         <v>-300</v>
@@ -2189,86 +2346,98 @@
         <v>-300</v>
       </c>
       <c r="O35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,19 +2482,21 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
       </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -2332,43 +2505,49 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" s="3">
         <v>100</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
-        <v>100</v>
-      </c>
-      <c r="N41" s="3">
-        <v>200</v>
+      <c r="N41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O41" s="3">
         <v>100</v>
       </c>
       <c r="P41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q41" s="3">
         <v>100</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41" s="3">
+        <v>100</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,43 +2602,49 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F43" s="3">
         <v>3400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2471,16 +2656,22 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2517,11 +2708,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2535,8 +2726,14 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2573,87 +2770,99 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F46" s="3">
         <v>3600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>900</v>
       </c>
       <c r="I46" s="3">
         <v>800</v>
       </c>
       <c r="J46" s="3">
+        <v>900</v>
+      </c>
+      <c r="K46" s="3">
         <v>800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
+        <v>800</v>
+      </c>
+      <c r="M46" s="3">
         <v>700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
-      </c>
-      <c r="R46" s="3">
-        <v>600</v>
-      </c>
-      <c r="S46" s="3">
-        <v>1100</v>
       </c>
       <c r="T46" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V46" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="E47" s="3">
         <v>10200</v>
@@ -2676,26 +2885,26 @@
       <c r="K47" s="3">
         <v>10200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
+      <c r="L47" s="3">
+        <v>10200</v>
       </c>
       <c r="M47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>10100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>10100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2703,8 +2912,14 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2715,10 +2930,10 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
@@ -2732,26 +2947,26 @@
       <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
+      <c r="L48" s="3">
+        <v>400</v>
       </c>
       <c r="M48" s="3">
+        <v>400</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2759,55 +2974,61 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2000</v>
       </c>
       <c r="H49" s="3">
         <v>2000</v>
       </c>
       <c r="I49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="J49" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="K49" s="3">
         <v>1900</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="M49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2815,8 +3036,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2956,35 +3195,41 @@
       <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>7600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>7700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>16100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>16100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>106100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>106100</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3284,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F54" s="3">
         <v>18000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>15700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>15000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>15400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>15100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>15000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>13200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>12700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>16600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>107200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,25 +3398,27 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>500</v>
@@ -3168,46 +3429,52 @@
       <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
+      <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
+        <v>500</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>300</v>
@@ -3216,34 +3483,34 @@
         <v>300</v>
       </c>
       <c r="I58" s="3">
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3251,8 +3518,14 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3260,16 +3533,16 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -3280,11 +3553,11 @@
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
@@ -3307,64 +3580,76 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>100</v>
-      </c>
-      <c r="R60" s="3">
-        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
       <c r="T60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3384,29 +3669,29 @@
         <v>300</v>
       </c>
       <c r="I61" s="3">
+        <v>300</v>
+      </c>
+      <c r="J61" s="3">
+        <v>300</v>
+      </c>
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>4700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3419,64 +3704,76 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>700</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>3700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>5300</v>
       </c>
       <c r="R62" s="3">
         <v>4900</v>
       </c>
       <c r="S62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U62" s="3">
         <v>8800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3952,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>5500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,32 +4162,38 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E70" s="3">
         <v>2200</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G70" s="3">
         <v>2100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>2000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>1600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>1500</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4286,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>400</v>
+      </c>
+      <c r="F72" s="3">
         <v>800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>1500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-3200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-3000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>5400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>5300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4534,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11900</v>
+        <v>10800</v>
       </c>
       <c r="E76" s="3">
-        <v>11800</v>
+        <v>11500</v>
       </c>
       <c r="F76" s="3">
         <v>11900</v>
       </c>
       <c r="G76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="H76" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I76" s="3">
         <v>12000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>12000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>7700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>98300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,80 +4658,92 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-100</v>
       </c>
       <c r="G81" s="3">
         <v>0</v>
@@ -4363,16 +4752,16 @@
         <v>-100</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-300</v>
       </c>
       <c r="M81" s="3">
         <v>-300</v>
@@ -4381,25 +4770,31 @@
         <v>-300</v>
       </c>
       <c r="O81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4815,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4449,11 +4846,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -4464,11 +4861,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4476,8 +4873,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>900</v>
+      </c>
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>200</v>
       </c>
       <c r="L89" s="3">
         <v>-300</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,13 +5273,15 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>4</v>
@@ -4872,11 +5313,11 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4890,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5455,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>8400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>90000</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5091,11 +5558,11 @@
       <c r="E96" s="3">
         <v>0</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
@@ -5118,11 +5585,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5789,76 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>200</v>
       </c>
       <c r="L100" s="3">
         <v>300</v>
       </c>
       <c r="M100" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N100" s="3">
         <v>300</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P100" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-90300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5398,11 +5895,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5416,13 +5913,19 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -5434,42 +5937,48 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
     </row>
